--- a/RobotOnTheFloor/01-ZigZagCrossRoted/01-Pwm-XYTheta/Ts-07/Resumo_Estatisticas.xlsx
+++ b/RobotOnTheFloor/01-ZigZagCrossRoted/01-Pwm-XYTheta/Ts-07/Resumo_Estatisticas.xlsx
@@ -473,16 +473,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.8592288302375861</v>
+        <v>-13.45951874065177</v>
       </c>
       <c r="D2" t="n">
-        <v>2.577515027631387</v>
+        <v>6.134548354519086</v>
       </c>
       <c r="E2" t="n">
-        <v>1.598623515392801</v>
+        <v>4.744400030901731</v>
       </c>
       <c r="F2" t="n">
-        <v>2.216228614485993</v>
+        <v>2.012843713872914</v>
       </c>
     </row>
     <row r="3">
@@ -497,16 +497,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-1.825381740394118</v>
+        <v>-2.546784217909175</v>
       </c>
       <c r="D3" t="n">
-        <v>2.34697198199674</v>
+        <v>2.561947392223251</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6517068098165255</v>
+        <v>0.8181065923639608</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5413560940273172</v>
+        <v>0.5909426460973308</v>
       </c>
     </row>
     <row r="4">
@@ -521,16 +521,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.8659891748798738</v>
+        <v>-0.680929578291114</v>
       </c>
       <c r="D4" t="n">
-        <v>2.445853315521143</v>
+        <v>1.771081420868919</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4395954271579298</v>
+        <v>0.3959985223595154</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5762015918829608</v>
+        <v>0.4172367686905079</v>
       </c>
     </row>
     <row r="5">
@@ -545,16 +545,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-1.314016189170486</v>
+        <v>-2.513328394503122</v>
       </c>
       <c r="D5" t="n">
-        <v>2.620257109477617</v>
+        <v>3.051415798895215</v>
       </c>
       <c r="E5" t="n">
-        <v>1.991420345703422</v>
+        <v>1.157927091190937</v>
       </c>
       <c r="F5" t="n">
-        <v>2.254968371962123</v>
+        <v>1.005689370101855</v>
       </c>
     </row>
     <row r="6">
@@ -569,16 +569,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-2.634979723277879</v>
+        <v>-1.68019525844228</v>
       </c>
       <c r="D6" t="n">
-        <v>2.529131018792308</v>
+        <v>1.348778336342187</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3546981537212025</v>
+        <v>0.2547304666468121</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2467904008211926</v>
+        <v>0.1281902629807802</v>
       </c>
     </row>
     <row r="7">
@@ -593,16 +593,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-2.199437864453994</v>
+        <v>-0.3587837018648116</v>
       </c>
       <c r="D7" t="n">
-        <v>1.252457428268662</v>
+        <v>0.5978094967458387</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3330524345796821</v>
+        <v>0.1414455411061714</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1303772766855944</v>
+        <v>0.06223027817420491</v>
       </c>
     </row>
     <row r="8">
@@ -617,16 +617,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-1.451607525378778</v>
+        <v>-0.3842054147848491</v>
       </c>
       <c r="D8" t="n">
-        <v>1.455288501613472</v>
+        <v>0.2440504025831157</v>
       </c>
       <c r="E8" t="n">
-        <v>0.201261613781703</v>
+        <v>0.1136345898358784</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1194700657918038</v>
+        <v>0.02003500860536938</v>
       </c>
     </row>
     <row r="9">
@@ -641,16 +641,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-2.906168431737216</v>
+        <v>-2.797504757979472</v>
       </c>
       <c r="D9" t="n">
-        <v>2.773365065145502</v>
+        <v>2.093611538675857</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3931440802516064</v>
+        <v>0.3474458219414612</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2791308354447107</v>
+        <v>0.1915511969676623</v>
       </c>
     </row>
     <row r="10">
@@ -665,16 +665,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.5977332675131068</v>
+        <v>-3.170130412410176</v>
       </c>
       <c r="D10" t="n">
-        <v>1.028983580656356</v>
+        <v>1.861060795394469</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1563213151819671</v>
+        <v>0.3094898006218429</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1006751689405702</v>
+        <v>0.1381202210841336</v>
       </c>
     </row>
     <row r="11">
@@ -689,16 +689,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.688418393021533</v>
+        <v>-1.221819488187321</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5602915337765545</v>
+        <v>0.4352999551514163</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1379108338410091</v>
+        <v>0.1814792941883154</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04576488442470852</v>
+        <v>0.03555551161608322</v>
       </c>
     </row>
     <row r="12">
@@ -713,16 +713,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.1285931790853642</v>
+        <v>-0.874009212695633</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4827724517724316</v>
+        <v>0.762675400955443</v>
       </c>
       <c r="E12" t="n">
-        <v>0.09199934860802182</v>
+        <v>0.197849755952644</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05096901931791542</v>
+        <v>0.08051995738754511</v>
       </c>
     </row>
     <row r="13">
@@ -737,16 +737,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.429139584904717</v>
+        <v>-5.008808277242985</v>
       </c>
       <c r="D13" t="n">
-        <v>1.027047911818622</v>
+        <v>2.688592205779524</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1443350574301665</v>
+        <v>0.4599145525267847</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1037260607022909</v>
+        <v>0.2057850116355256</v>
       </c>
     </row>
   </sheetData>
@@ -807,16 +807,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7409661151874343</v>
+        <v>-7.339329505012269</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1051949349914886</v>
+        <v>4.006155122950832</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2227254939307288</v>
+        <v>2.736267774254879</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09044991882796966</v>
+        <v>1.314483754959905</v>
       </c>
     </row>
     <row r="3">
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-1.857788079791729</v>
+        <v>0.6163672934647352</v>
       </c>
       <c r="D3" t="n">
-        <v>3.899323676645399</v>
+        <v>0.1476879856720089</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6591817048952</v>
+        <v>0.088489298186836</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8994238751589508</v>
+        <v>0.03406593332662639</v>
       </c>
     </row>
     <row r="4">
@@ -855,16 +855,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.5761820130065999</v>
+        <v>0.7630956901936996</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1537033811682323</v>
+        <v>0.069173925654666</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0998443354000548</v>
+        <v>0.05581064063330351</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03620991183114283</v>
+        <v>0.01629620461132171</v>
       </c>
     </row>
     <row r="5">
@@ -879,16 +879,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.7531351918290407</v>
+        <v>0.5064310331560495</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1149441614297879</v>
+        <v>0.1878627425482498</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2124495083182849</v>
+        <v>0.1626710668361986</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09891985318095529</v>
+        <v>0.06191603362850785</v>
       </c>
     </row>
     <row r="6">
@@ -903,16 +903,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-5.825631596062778</v>
+        <v>-0.936579560441287</v>
       </c>
       <c r="D6" t="n">
-        <v>2.463625637066548</v>
+        <v>2.982508614756965</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6660391829975261</v>
+        <v>0.1840559241256904</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2403984427565744</v>
+        <v>0.2834628592159867</v>
       </c>
     </row>
     <row r="7">
@@ -927,16 +927,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-3.80845549162215</v>
+        <v>0.643142521757028</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9282822312210871</v>
+        <v>0.09403616879144412</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5005466197188053</v>
+        <v>0.03714785439256239</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09663155534917814</v>
+        <v>0.009788899263365186</v>
       </c>
     </row>
     <row r="8">
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-2.303460680303947</v>
+        <v>-0.8821382042698577</v>
       </c>
       <c r="D8" t="n">
-        <v>2.280359933162299</v>
+        <v>0.3124290891620046</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2711934192972639</v>
+        <v>0.1545117513428347</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1872032596573434</v>
+        <v>0.02564847024907771</v>
       </c>
     </row>
     <row r="9">
@@ -975,16 +975,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-4.920501644547484</v>
+        <v>-5.155961694315265</v>
       </c>
       <c r="D9" t="n">
-        <v>1.443190540009187</v>
+        <v>2.499278629071001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.595880647327481</v>
+        <v>0.5632285690300325</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1452527783671109</v>
+        <v>0.2286669728888847</v>
       </c>
     </row>
     <row r="10">
@@ -999,16 +999,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.2020352677853254</v>
+        <v>-6.500217322785252</v>
       </c>
       <c r="D10" t="n">
-        <v>0.05591654500393565</v>
+        <v>1.14572885228893</v>
       </c>
       <c r="E10" t="n">
-        <v>0.07807241605651855</v>
+        <v>0.5566350531727645</v>
       </c>
       <c r="F10" t="n">
-        <v>0.005470842995622336</v>
+        <v>0.08503124818503066</v>
       </c>
     </row>
     <row r="11">
@@ -1023,16 +1023,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.9689472869510244</v>
+        <v>-2.153675562019204</v>
       </c>
       <c r="D11" t="n">
-        <v>0.920510839322614</v>
+        <v>0.2079651504045084</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1608245700560461</v>
+        <v>0.2575937505891258</v>
       </c>
       <c r="F11" t="n">
-        <v>0.07518777213951483</v>
+        <v>0.01698669442402293</v>
       </c>
     </row>
     <row r="12">
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6840984609175035</v>
+        <v>0.3035461700454264</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1364607459396238</v>
+        <v>0.1442740706279252</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0333515128896475</v>
+        <v>0.07352857144741065</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01440693306007526</v>
+        <v>0.01523182995614526</v>
       </c>
     </row>
     <row r="13">
@@ -1071,16 +1071,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2191968066280824</v>
+        <v>-8.337349495005544</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0666726214639274</v>
+        <v>0.6357533372740889</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07885672956466802</v>
+        <v>0.7146813006242329</v>
       </c>
       <c r="F13" t="n">
-        <v>0.006733559653417138</v>
+        <v>0.04866059926345002</v>
       </c>
     </row>
   </sheetData>
